--- a/docs/LTT_GKD_项目进度跟踪_v3.xlsx
+++ b/docs/LTT_GKD_项目进度跟踪_v3.xlsx
@@ -3250,7 +3250,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>首页电源圆脉冲/规则三Tab/卡片式设置/步骤编辑器/跳过记录页；单Activity；移除上传小FAB(导出在三点菜单)；Logger补clear()+LogViewer加返回/清空/自动刷新；全部42个.kt文件中文注释补全</t>
+          <t>首页电源圆脉冲/规则三Tab/卡片式设置/步骤编辑器/跳过记录页；单Activity；移除上传小FAB(导出在三点菜单)；Logger补clear()+LogViewer加返回/清空/自动刷新；全部42个.kt文件逐行中文注释补全；深色模式适配（徽章色深色变体）；7天趋势柱状图（Canvas绘制）</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4574,6 +4574,60 @@
       <c r="E49" s="10" t="inlineStr">
         <is>
           <t>KDoc+行内注释；数据层8+工具服务层13+UI/Theme7+已有14=42</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>十四·UI优化</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>深色模式适配：Color.kt增加深色徽章变体，HistoryScreen/SettingsScreen/RulesScreen按isSystemInDarkTheme切换</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Color.kt,HistoryScreen.kt,SettingsScreen.kt,RulesScreen.kt</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>8个深色变体色值+3个Screen适配</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>十五·UI优化</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>7天趋势柱状图：SkipHistoryStore.dailyCounts7d() + Canvas绘制柱状图</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>SkipHistoryStore.kt,HistoryScreen.kt</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>纯Canvas无第三方依赖，含网格线/标签/数值</t>
         </is>
       </c>
     </row>

--- a/docs/LTT_GKD_项目进度跟踪_v3.xlsx
+++ b/docs/LTT_GKD_项目进度跟踪_v3.xlsx
@@ -3250,7 +3250,7 @@
       </c>
       <c r="H63" s="10" t="inlineStr">
         <is>
-          <t>首页电源圆脉冲/规则三Tab/卡片式设置/步骤编辑器/跳过记录页；单Activity；移除上传小FAB(导出在三点菜单)；Logger补clear()+LogViewer加返回/清空/自动刷新；全部42个.kt文件逐行中文注释补全；深色模式适配（徽章色深色变体）；7天趋势柱状图（Canvas绘制）</t>
+          <t>首页电源圆脉冲/规则三Tab/卡片式设置/步骤编辑器/跳过记录页；单Activity；移除上传小FAB(导出在三点菜单)；Logger补clear()+LogViewer加返回/清空/自动刷新；全部42个.kt文件逐行中文注释补全；深色模式适配（徽章色深色变体）；7天趋势柱状图（Canvas绘制）；CI(GitHub Actions)；规则上传去重；Instrumented测试3文件</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4628,6 +4628,87 @@
       <c r="E51" s="10" t="inlineStr">
         <is>
           <t>纯Canvas无第三方依赖，含网格线/标签/数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>十六·CI</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>GitHub Actions CI：push/PR触发，JDK17，Gradle缓存，assembleDebug+testDebugUnitTest，APK artifact</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>.github/workflows/ci.yml</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>CI自动构建+测试+APK上传</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>十七·规则共享</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>规则上传去重：GistClient.checkRuleExists()上传前检查同ID，非创建者提示已存在</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>GistClient.kt,RuleEditActivity.kt</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>同ID只保留第一个创建者，自己可覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>十八·测试</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Instrumented测试：RuleEngine节流/SkipHistoryStore记录/WhitelistStore白名单 16个测试</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>app/src/androidTest/</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>androidTestImplementation依赖+3文件16测试</t>
         </is>
       </c>
     </row>

--- a/docs/LTT_GKD_项目进度跟踪_v3.xlsx
+++ b/docs/LTT_GKD_项目进度跟踪_v3.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4709,6 +4709,303 @@
       <c r="E54" s="10" t="inlineStr">
         <is>
           <t>androidTestImplementation依赖+3文件16测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>十九·修复</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>DataStore多实例崩溃：dataStore从类内部移到文件顶层；Logger复用App.settings</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>SettingsStore.kt,WhitelistStore.kt,Logger.kt</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>顶层委托保证单例</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>二十·修复</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Toast在非主线程崩溃：MainActivity.toast用runOnUiThread；RuleEditActivity用withContext(Main)</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>MainActivity.kt,RuleEditActivity.kt</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>所有Toast切主线程</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>二十一·修复</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>内置规则只显示已安装应用：reload时getInstalledPackages过滤未安装包名</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>RuleRepository.kt</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>未安装应用规则不显示不启用</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>二十二·修复</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>无障碍服务状态检测：isAccessibilityEnabled同时检查实例+系统设置</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>MainActivity.kt</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>崩溃后不误显示关闭</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>二十三·优化</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>同步按钮交互：无订阅源跳转设置；有则显示loading+同步中/成功/失败反馈</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>RulesScreen.kt,MainActivity.kt,SettingsScreen.kt</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>onSyncSubscribed带完成回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>二十四·更名</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>APP更名小狐+狐狸图标+QUERY_ALL_PACKAGES权限</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>strings.xml,ic_launcher,AndroidManifest.xml</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>OPPO读取应用列表权限</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>二十五·修复</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>输入框光标跳开头：改用本地mutableStateOf，Flow仅初始化</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>SettingsScreen.kt</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>4个输入框修复</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>二十六·优化</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>同步按钮反馈：loading动画+同步中/成功/失败Toast+无订阅源跳转</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>RulesScreen.kt,MainActivity.kt</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>onSyncSubscribed带回调</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>二十七·优化</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>无订阅源引导：订阅卡片自动展开+蓝色提示横幅</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>SettingsScreen.kt</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>引导用户配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>二十八·修复</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>无障碍崩溃保护：全局UncaughtExceptionHandler吞非主线程异常</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>App.kt,SkipAccessibilityService.kt</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>服务不中断</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>二十九·限制</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>规则导入仅选择JSON/文本格式</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>MainActivity.kt</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>application/json,text/plain</t>
         </is>
       </c>
     </row>

--- a/docs/LTT_GKD_项目进度跟踪_v3.xlsx
+++ b/docs/LTT_GKD_项目进度跟踪_v3.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="项目总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="功能清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="开发步骤" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="规则统计" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="源文件清单" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能清单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开发步骤" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="规则统计" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="源文件清单" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,7 +696,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5006,6 +5006,303 @@
       <c r="E65" s="10" t="inlineStr">
         <is>
           <t>application/json,text/plain</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>三十·收敛</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>移除内置高危弹窗关键词规则（关闭/取消/×/以后再说），规则数 112→89</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>assets/rules/*.json + 开发文档§5.15</t>
+        </is>
+      </c>
+      <c r="D66" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>安全优先：宁漏关延迟弹窗不误点功能按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>三十一·修复</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>跨窗口误点：服务重连/窗口切换瞬间事件包名与活动窗口错位校验</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>WindowEventProcessor.kt §5.16</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>root.packageName 不一致即跳过；曾误点自身界面卡死UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>三十二·修复</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>明文 HTTP 订阅源被禁：usesCleartextTraffic 改 true</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>AndroidManifest.xml §5.17</t>
+        </is>
+      </c>
+      <c r="D68" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>订阅源常为自建/内网 http；Gist 仍走 HTTPS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>三十三·测试</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>订阅消费侧真机全链路验证（URL源添加/同步/落地/合并/展示/删除清理）+ SubscriptionSyncerTest 5 用例</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>SubscriptionSyncerTest.kt</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>adb reverse+本地server；WorkManager排程与系统Job注册确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>三十四·优化</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>设置开关改 StateFlow 常驻快照，事件处理不再锁内读 DataStore</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>WindowEventProcessor.kt</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>OCR/通知开关 Eagerly stateIn，零 I/O</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>三十五·实证</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>ID 精确规则路线：机制可用（窗口外命中验证），主流电商不可行（淘宝零ID/京东混淆）</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>开发文档§5.18</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>不再作为内置补全方案；改社区积累+评估activity限定DESC精确相等</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>三十六·验证</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>深色模式全页面验证 + 订阅自动更新排程随间隔实时变化验证</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>真机 OnePlus PJD110</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>徽章深色变体正常；Job约束=有网络、延迟≈间隔</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>三十七·兜底</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>服务看门狗：崩溃/被系统移除后启动即查+15分钟周期检查，掉绑发高优先级通知引导重开</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>ServiceWatchdogWorker.kt §5.19</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>am crash 实测系统直接移除服务不重绑；G7 最后兜底</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>三十八·修复</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>跳过历史记录实际包名（通用规则原记空串）+ androidTest getTargetContext 编译修复</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>SkipHistoryStore.kt,androidTest</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>新版androidx.test改 getInstrumentation().targetContext</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>三十九·UI</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>主题色统一文档规定 #007070（禁用动态取色）+ 吉祥物图标替换（mascot_icon_v6 五密度）+ 设置页日志改纯入口</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Theme.kt,drawable-*,SettingsScreen.kt</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>dynamicColor默认false；日志开关移除，logEnabled默认true</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>四十·修复</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>历史页系统返回键回首页（BackHandler 拦截）+ 贡献者卡片改下拉展开（与规则订阅一致）</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>MainActivity.kt,SettingsScreen.kt</t>
+        </is>
+      </c>
+      <c r="D76" s="8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>返回键不再退出应用；设备ID/Token/Gist收进折叠卡片</t>
         </is>
       </c>
     </row>
